--- a/T7_PopularGraphs/auto_dataset.xlsx
+++ b/T7_PopularGraphs/auto_dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanvazquez/Documents/GitHub/TEC-IN2039/Session_7_Multivariate_Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanvazquez/Documents/GitHub/TEC-IN2039-EN/T7_PopularGraphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C678C6-8324-3643-B47E-341203A6D9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6017C94F-5586-DA47-A56D-42FBA7C694D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="1500" windowWidth="27240" windowHeight="15940" xr2:uid="{B26D55B1-590C-FA4C-964A-1DD3B3123C93}"/>
   </bookViews>
@@ -12939,7 +12939,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I399" xr:uid="{D3A12E88-F8A6-0941-AFDD-0E9CFEB713DC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>